--- a/results/block3_results/cad-rads/Normal_1/patient_report_Normal_1.xlsx
+++ b/results/block3_results/cad-rads/Normal_1/patient_report_Normal_1.xlsx
@@ -799,10 +799,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>115</v>
+        <v>460</v>
       </c>
       <c r="E2" t="n">
-        <v>89</v>
+        <v>356</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>405</v>
+        <v>1246</v>
       </c>
       <c r="E3" t="n">
-        <v>405</v>
+        <v>1246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>333</v>
+        <v>925</v>
       </c>
       <c r="E4" t="n">
-        <v>333</v>
+        <v>925</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>363</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>215</v>
+        <v>776</v>
       </c>
       <c r="E7" t="n">
-        <v>215</v>
+        <v>776</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="E12" t="n">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>606</v>
+        <v>804</v>
       </c>
       <c r="E15" t="n">
-        <v>535</v>
+        <v>729</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>

--- a/results/block3_results/cad-rads/Normal_1/patient_report_Normal_1.xlsx
+++ b/results/block3_results/cad-rads/Normal_1/patient_report_Normal_1.xlsx
@@ -531,16 +531,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Left main stenosis is &gt;=50%, meeting the CAD-RADS 4B criterion.</t>
+          <t>RCA, LAD, and LCX each have at least one segment with &gt;=70% stenosis.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>First diagonal (D1) (segment 9)</t>
+          <t>LCX posterolateral branch (segment 17)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.80868804884203</v>
+        <v>93.27278844286676</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -549,13 +549,13 @@
         <v>3</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
         <v>17</v>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>86.84242426320652</v>
+        <v>86.1559559717453</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -672,11 +672,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>First diagonal (D1) (segment 9)</t>
+          <t>Second diagonal (D2) (segment 10)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>91.80868804884203</v>
+        <v>92.69234155339068</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88.00096534996815</v>
+        <v>93.27278844286676</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -793,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>16.76285285900079</v>
+        <v>15.82507038827767</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -802,7 +802,7 @@
         <v>460</v>
       </c>
       <c r="E2" t="n">
-        <v>356</v>
+        <v>228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16.76285285900079</v>
+        <v>15.82507038827767</v>
       </c>
     </row>
     <row r="3">
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>40.16755430681539</v>
+        <v>34.38341661144862</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>40.16755430681539</v>
+        <v>34.38341661144862</v>
       </c>
     </row>
     <row r="4">
@@ -879,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>63.76964624909517</v>
+        <v>64.31046045191174</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>63.76964624909517</v>
+        <v>64.31046045191174</v>
       </c>
     </row>
     <row r="5">
@@ -922,16 +922,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>86.84242426320652</v>
+        <v>86.1559559717453</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.002281363792481</v>
       </c>
       <c r="D5" t="n">
         <v>259</v>
       </c>
       <c r="E5" t="n">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -957,24 +957,20 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>86.84242426320652</v>
+        <v>86.1559559717453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>73.49159409819676</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>363</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -991,24 +987,20 @@
           <t>LCA</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>73.49159409819676</v>
-      </c>
+          <t>Not assessable</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>79.10915580861952</v>
+        <v>77.8576911786642</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1017,7 +1009,7 @@
         <v>776</v>
       </c>
       <c r="E7" t="n">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1043,7 +1035,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>79.10915580861952</v>
+        <v>77.8576911786642</v>
       </c>
     </row>
     <row r="8">
@@ -1051,7 +1043,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>84.71822983802619</v>
+        <v>85.50953385499778</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1060,7 +1052,7 @@
         <v>206</v>
       </c>
       <c r="E8" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1086,7 +1078,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>84.71822983802619</v>
+        <v>85.50953385499778</v>
       </c>
     </row>
     <row r="9">
@@ -1094,7 +1086,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>57.17407343198862</v>
+        <v>65.61645780401632</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1129,24 +1121,20 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>57.17407343198862</v>
+        <v>65.61645780401632</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>91.80868804884203</v>
-      </c>
-      <c r="C10" t="n">
-        <v>78.43188078620044</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>71</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1163,33 +1151,29 @@
           <t>LAD</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>91.80868804884203</v>
-      </c>
+          <t>Not assessable</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>90.35137770105396</v>
+        <v>92.69234155339068</v>
       </c>
       <c r="C11" t="n">
-        <v>15.41770768654991</v>
+        <v>46.99688231106188</v>
       </c>
       <c r="D11" t="n">
         <v>233</v>
       </c>
       <c r="E11" t="n">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1215,7 +1199,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>90.35137770105396</v>
+        <v>92.69234155339068</v>
       </c>
     </row>
     <row r="12">
@@ -1223,7 +1207,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>51.77940351438588</v>
+        <v>50.13626362211434</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1232,7 +1216,7 @@
         <v>268</v>
       </c>
       <c r="E12" t="n">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1258,7 +1242,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>51.77940351438588</v>
+        <v>50.13626362211434</v>
       </c>
     </row>
     <row r="13">
@@ -1266,7 +1250,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>71.02875962329487</v>
+        <v>65.51280273104059</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1275,7 +1259,7 @@
         <v>635</v>
       </c>
       <c r="E13" t="n">
-        <v>594</v>
+        <v>557</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1293,15 +1277,15 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
+          <t>Moderate stenosis</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>71.02875962329487</v>
+        <v>65.51280273104059</v>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1293,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>78.66652148198055</v>
+        <v>79.90736409423839</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1318,7 +1302,7 @@
         <v>271</v>
       </c>
       <c r="E14" t="n">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1344,7 +1328,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>78.66652148198055</v>
+        <v>79.90736409423839</v>
       </c>
     </row>
     <row r="15">
@@ -1352,7 +1336,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>49.06734541364825</v>
+        <v>45.79088806727626</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1361,7 +1345,7 @@
         <v>804</v>
       </c>
       <c r="E15" t="n">
-        <v>729</v>
+        <v>664</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1387,7 +1371,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>49.06734541364825</v>
+        <v>45.79088806727626</v>
       </c>
     </row>
     <row r="16">
@@ -1395,16 +1379,16 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>88.00096534996815</v>
+        <v>93.27278844286676</v>
       </c>
       <c r="C16" t="n">
-        <v>16.33264754485299</v>
+        <v>58.95557371455138</v>
       </c>
       <c r="D16" t="n">
         <v>160</v>
       </c>
       <c r="E16" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1430,7 +1414,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>88.00096534996815</v>
+        <v>93.27278844286676</v>
       </c>
     </row>
     <row r="17">
@@ -1438,16 +1422,16 @@
         <v>19</v>
       </c>
       <c r="B17" t="n">
-        <v>82.73888446055896</v>
+        <v>83.54090399876489</v>
       </c>
       <c r="C17" t="n">
-        <v>7.32048232511238</v>
+        <v>8.564141719289397</v>
       </c>
       <c r="D17" t="n">
         <v>373</v>
       </c>
       <c r="E17" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1473,7 +1457,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>82.73888446055896</v>
+        <v>83.54090399876489</v>
       </c>
     </row>
   </sheetData>
@@ -1552,16 +1536,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>82.73888446055896</v>
+        <v>83.54090399876489</v>
       </c>
       <c r="C2" t="n">
-        <v>7.32048232511238</v>
+        <v>8.564141719289397</v>
       </c>
       <c r="D2" t="n">
         <v>373</v>
       </c>
       <c r="E2" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1587,7 +1571,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>82.73888446055896</v>
+        <v>83.54090399876489</v>
       </c>
     </row>
   </sheetData>
